--- a/public/templates/template-import-hc-dashboard.xlsx
+++ b/public/templates/template-import-hc-dashboard.xlsx
@@ -507,13 +507,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋  Template Import — HC Dashboard 5758 Creative Lab</t>
+          <t>📋  Template Import — HC Dashboard</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Workforce</t>
@@ -537,11 +537,11 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Data karyawan. Status: active / resigned / end_contract | Tipe Kontrak: PKWTT / PKWT | Level: Staff / Jr. Staff / Sr. Staff / Manager / Sr. Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>Data karyawan. Status: active / resigned / end_contract | Tipe: PKWTT / PKWT | Tanggal format YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Recruitment</t>
@@ -549,11 +549,11 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Posisi lowongan. Hiring Process: Open / Screening / Interview / Offering / OL Signed / Joined / On Hold / Cancelled | Source: Job Portal / LinkedIn / Referral / Internal / Headhunter</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
+          <t>Posisi lowongan. Hiring Process: Open / Screening / Interview / Offering / OL Signed / Joined / On Hold / Cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Learning TNA</t>
@@ -561,11 +561,11 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Data training. Kategori: Hard Skill / Soft Skill / Leadership / Technical / Compliance / Others | Metode: Online / Offline / Hybrid | Status: Planned / In Progress / Done / Overdue</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+          <t>Data training. Kategori: Hard Skill / Soft Skill / Leadership / Technical / Compliance | Status: Planned / In Progress / Done / Overdue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
@@ -573,11 +573,11 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Data gaji bulanan. Bulan pakai nama Indonesia (Januari s.d. Desember). BPJS &amp; PPh21 bisa dikosongkan → auto-kalkulasi. Nama karyawan harus sama persis dengan data di sistem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
+          <t>Data gaji bulanan. BPJS &amp; PPh21 bisa dikosongkan (auto-kalkulasi). Bulan pakai nama Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Saldo Cuti</t>
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Override saldo cuti per karyawan per tahun. Carry-over maksimal 5 hari (hangus setelah Juli). Nama karyawan harus sama persis.</t>
+          <t>Override saldo cuti per karyawan. Carry-over maksimal 5 hari (hangus setelah Juli).</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>• Nama karyawan di sheet Payroll, TNA, dan Saldo Cuti harus sama persis dengan data di sistem</t>
+          <t>• Nama karyawan di sheet Payroll, TNA, dan Saldo Cuti harus sama persis dengan yang ada di sistem</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>• Hapus baris contoh sebelum import — atau biarkan sistem melewati baris yang tidak dikenali</t>
+          <t>• Tanggal lahir (birth_date) format YYYY-MM-DD, contoh: 1995-08-17</t>
         </is>
       </c>
     </row>
@@ -658,10 +658,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -673,9 +673,10 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -741,15 +742,20 @@
       </c>
       <c r="M1" s="8" t="inlineStr">
         <is>
+          <t>Tgl Lahir</t>
+        </is>
+      </c>
+      <c r="N1" s="8" t="inlineStr">
+        <is>
           <t>Join Date</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>Catatan</t>
         </is>
@@ -818,11 +824,16 @@
       </c>
       <c r="M2" s="9" t="inlineStr">
         <is>
+          <t>1995-08-17</t>
+        </is>
+      </c>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
           <t>2024-01-15</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr"/>
       <c r="O2" s="9" t="inlineStr"/>
+      <c r="P2" s="9" t="inlineStr"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -887,15 +898,20 @@
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
+          <t>1998-03-22</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
           <t>2024-03-01</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr">
+      <c r="O3" s="10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="O3" s="10" t="inlineStr">
+      <c r="P3" s="10" t="inlineStr">
         <is>
           <t>Kontrak 1 tahun</t>
         </is>
@@ -947,6 +963,13 @@
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Status Pernikahan: Belum Kawin | Kawin | Cerai</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Tgl Lahir format: YYYY-MM-DD (contoh: 1995-08-17) — digunakan untuk reminder ulang tahun di Dashboard</t>
         </is>
       </c>
     </row>
@@ -961,7 +984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1167,7 @@
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>Kandidat sudah selected</t>
+          <t>Sudah selected</t>
         </is>
       </c>
     </row>
@@ -1164,13 +1187,6 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Division: Creative | Marketing | Social Media | Human Capital | Finance | IT &amp; Systems | Operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Budget Allocation: angka dalam rupiah tanpa titik/koma (contoh: 5000000)</t>
         </is>
@@ -1668,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1817,7 +1833,7 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Hak Tahunan: default 12 hari (sesuai kebijakan perusahaan)</t>
+          <t>Hak Tahunan: default 12 hari/tahun</t>
         </is>
       </c>
     </row>
@@ -1832,13 +1848,6 @@
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Hak OT: jumlah hari overtime leave yang disetujui HC + atasan</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Terpakai &amp; OT Terpakai: akan dihitung ulang otomatis dari data cuti yang ada</t>
         </is>
       </c>
     </row>

--- a/public/templates/template-import-hc-dashboard.xlsx
+++ b/public/templates/template-import-hc-dashboard.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Workforce</t>
@@ -537,11 +537,11 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Data karyawan. Status: active / resigned / end_contract | Tipe: PKWTT / PKWT | Tanggal format YYYY-MM-DD</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
+          <t>Data karyawan. Kolom wajib: Employee ID, Nama Lengkap, Join Date. Tanggal format YYYY-MM-DD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Recruitment</t>
@@ -549,11 +549,11 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Posisi lowongan. Hiring Process: Open / Screening / Interview / Offering / OL Signed / Joined / On Hold / Cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
+          <t>Posisi lowongan. Hiring Process: Open / Screening / Interview / Offering / OL Signed / Joined.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Learning TNA</t>
@@ -561,11 +561,11 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Data training. Kategori: Hard Skill / Soft Skill / Leadership / Technical / Compliance | Status: Planned / In Progress / Done / Overdue</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
+          <t>Data training. Status: Planned / In Progress / Done / Overdue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
@@ -573,11 +573,11 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Data gaji bulanan. BPJS &amp; PPh21 bisa dikosongkan (auto-kalkulasi). Bulan pakai nama Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
+          <t>Data gaji bulanan. BPJS &amp; PPh21 bisa dikosongkan (auto-kalkulasi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Saldo Cuti</t>
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Override saldo cuti per karyawan. Carry-over maksimal 5 hari (hangus setelah Juli).</t>
+          <t>Override saldo cuti. Carry-over maksimal 5 hari.</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>• Baris pertama (header) JANGAN diubah, dipindah, atau dihapus</t>
+          <t>• Baris pertama (header) JANGAN diubah</t>
         </is>
       </c>
     </row>
@@ -613,28 +613,28 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>• Angka tanpa titik/koma  (contoh: 8000000  bukan  8.000.000)</t>
+          <t>• Angka tanpa titik/koma  (contoh: 8000000 bukan 8.000.000)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>• Nama karyawan di sheet Payroll, TNA, dan Saldo Cuti harus sama persis dengan yang ada di sistem</t>
+          <t>• Nama karyawan di Payroll, TNA, Saldo Cuti harus sama persis dengan sistem</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>• Kolom yang dikosongkan akan diisi default atau dihitung otomatis oleh sistem</t>
+          <t>• Tgl Lahir format YYYY-MM-DD — untuk reminder ulang tahun di Dashboard</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>• Tanggal lahir (birth_date) format YYYY-MM-DD, contoh: 1995-08-17</t>
+          <t>• Kolom kosong diisi default atau dihitung otomatis</t>
         </is>
       </c>
     </row>
@@ -658,25 +658,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -697,65 +696,60 @@
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>No HP</t>
+          <t>Posisi</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>Posisi</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Divisi</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>Divisi</t>
+          <t>Entitas</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>Entitas</t>
+          <t>Tipe Kontrak</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>Tipe Kontrak</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Status Pernikahan</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>Status Pernikahan</t>
+          <t>Tgl Lahir</t>
         </is>
       </c>
       <c r="M1" s="8" t="inlineStr">
         <is>
-          <t>Tgl Lahir</t>
+          <t>Join Date</t>
         </is>
       </c>
       <c r="N1" s="8" t="inlineStr">
         <is>
-          <t>Join Date</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="O1" s="8" t="inlineStr">
-        <is>
-          <t>End Date</t>
-        </is>
-      </c>
-      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>Catatan</t>
         </is>
@@ -779,61 +773,56 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>08123456789</t>
+          <t>Staff IT</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Staff IT</t>
+          <t>Staff</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>Staff</t>
+          <t>IT &amp; Systems</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>IT &amp; Systems</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>SSR</t>
+          <t>PKWTT</t>
         </is>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>PKWTT</t>
+          <t>active</t>
         </is>
       </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Laki-laki</t>
         </is>
       </c>
       <c r="K2" s="9" t="inlineStr">
         <is>
-          <t>Laki-laki</t>
+          <t>Belum Kawin</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Belum Kawin</t>
+          <t>1995-08-17</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
         <is>
-          <t>1995-08-17</t>
-        </is>
-      </c>
-      <c r="N2" s="9" t="inlineStr">
-        <is>
           <t>2024-01-15</t>
         </is>
       </c>
+      <c r="N2" s="9" t="inlineStr"/>
       <c r="O2" s="9" t="inlineStr"/>
-      <c r="P2" s="9" t="inlineStr"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -853,123 +842,107 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>08234567890</t>
+          <t>Content Creator</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>Content Creator</t>
+          <t>Jr. Staff</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Jr. Staff</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>SSR</t>
+          <t>PKWT</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>PKWT</t>
+          <t>active</t>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Kawin</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>Kawin</t>
+          <t>1998-03-22</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>1998-03-22</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="O3" s="10" t="inlineStr">
-        <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="P3" s="10" t="inlineStr">
-        <is>
-          <t>Kontrak 1 tahun</t>
-        </is>
-      </c>
+      <c r="O3" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Status: active | resigned | end_contract</t>
+          <t>Kolom wajib: Employee ID, Nama Lengkap, Join Date</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Tipe Kontrak: PKWTT | PKWT</t>
+          <t>Status: active | resigned | end_contract</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Level: Staff | Jr. Staff | Sr. Staff | Manager | Sr. Manager | Head | Director</t>
+          <t>Tipe Kontrak: PKWTT | PKWT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Divisi: Creative | Marketing | Social Media | Human Capital | Finance | IT &amp; Systems | Operations</t>
+          <t>Level: Staff | Jr. Staff | Sr. Staff | Manager | Sr. Manager | Head | Director</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Entitas: SSR | Nyambee (PAT) | PAT-5758</t>
+          <t>Gender: Laki-laki | Perempuan</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Gender: Laki-laki | Perempuan</t>
+          <t>Status Pernikahan: Belum Kawin | Kawin | Cerai</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Status Pernikahan: Belum Kawin | Kawin | Cerai</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Tgl Lahir format: YYYY-MM-DD (contoh: 1995-08-17) — digunakan untuk reminder ulang tahun di Dashboard</t>
+          <t>Tgl Lahir: YYYY-MM-DD — digunakan untuk reminder ulang tahun di Dashboard</t>
         </is>
       </c>
     </row>
@@ -984,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1130,7 @@
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>Nama Kandidat Final</t>
+          <t>Nama Kandidat</t>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
@@ -1165,30 +1138,12 @@
           <t>5000000</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>Sudah selected</t>
-        </is>
-      </c>
+      <c r="L3" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Hiring Process: Open | Screening | Interview | Offering | OL Signed | Joined | On Hold | Cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Source: Job Portal | LinkedIn | Referral | Internal | Headhunter</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Budget Allocation: angka dalam rupiah tanpa titik/koma (contoh: 5000000)</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1408,51 +1363,19 @@
           <t>8</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
-        <is>
-          <t>Lulus dengan nilai baik</t>
-        </is>
-      </c>
+      <c r="M3" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Nama: harus sama persis dengan yang ada di sistem</t>
+          <t>Status: Planned | In Progress | Done | Overdue</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Kategori: Hard Skill | Soft Skill | Leadership | Technical | Compliance | Others</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Metode: Online | Offline | Hybrid</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Status: Planned | In Progress | Done | Overdue</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Score: 0–100 (kosongkan jika belum ada nilai)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Quarter: Q1 | Q2 | Q3 | Q4</t>
+          <t>Score: 0–100</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1641,35 +1564,14 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Nama: harus sama persis dengan yang ada di sistem</t>
+          <t>Bulan: Januari | Februari | ... | Desember</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Bulan: Januari | Februari | Maret | April | Mei | Juni | Juli | Agustus | September | Oktober | November | Desember</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>BPJS &amp; PPh21: dikosongkan → sistem auto-kalkulasi sesuai aturan 2024–2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Net Salary: dikosongkan → dihitung otomatis dari komponen di atas</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Tgl Bayar format: YYYY-MM-DD</t>
+          <t>BPJS &amp; PPh21 dikosongkan → auto-kalkulasi</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1817,37 +1719,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>OT kompensasi April 2026</t>
-        </is>
-      </c>
+      <c r="H3" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Nama: harus sama persis dengan yang ada di sistem</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Hak Tahunan: default 12 hari/tahun</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Carry-over: sisa cuti tahun lalu, maksimal 5 hari, hangus setelah Juli</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Hak OT: jumlah hari overtime leave yang disetujui HC + atasan</t>
+          <t>Carry-over maksimal 5 hari, hangus setelah Juli</t>
         </is>
       </c>
     </row>

--- a/public/templates/template-import-hc-dashboard.xlsx
+++ b/public/templates/template-import-hc-dashboard.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Learning TNA" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saldo Cuti" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manajemen Cuti" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1731,4 +1732,275 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Nama</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Divisi</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Tipe Cuti</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Cuti Khusus</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Tanggal Mulai</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>Tanggal Selesai</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Total Hari</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>Catatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Budi Santoso</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Creative</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Tahunan</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr"/>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Sari Dewi</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Penting</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Menikah (2hr)</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Ahmad Rivai</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Finance &amp; Accounting</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Sakit</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr"/>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Lampiran surat dokter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Winda Silvia</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Community Activation and Network</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Tahunan</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Tipe Cuti: Tahunan | Penting | Sakit | Melahirkan | Cuti Bersama | Overtime | Unpaid</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Cuti Khusus (isi jika Tipe = Penting): Menikah (2hr) | Ulang Tahun (1hr) | Khitan/Baptis anak (1hr) | Istri melahirkan/keguguran (2hr) | Kedukaan keluarga inti (2hr) | Keluarga serumah (1hr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Tanggal format: YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Status: Approved | Pending | Rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Nama harus sama persis dengan yang ada di sistem</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>